--- a/ET/Packages/cn.etetet.statesync/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET/Packages/cn.etetet.statesync/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -1,15 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20452" windowHeight="8707" activeTab="2"/>
+    <workbookView windowWidth="21000" windowHeight="11025"/>
   </bookViews>
   <sheets>
-    <sheet name="Router" sheetId="3" r:id="rId1"/>
-    <sheet name="Realm" sheetId="4" r:id="rId2"/>
-    <sheet name="Game" sheetId="1" r:id="rId3"/>
+    <sheet name="Scene" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+  <si>
+    <t>Realm应该是所有区共用的，所以单独放到一个zone</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
@@ -68,27 +69,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>RouterManager</t>
-  </si>
-  <si>
-    <t>Router</t>
-  </si>
-  <si>
-    <t>Router01</t>
-  </si>
-  <si>
-    <t>Router02</t>
-  </si>
-  <si>
-    <t>Router03</t>
-  </si>
-  <si>
-    <t>Router04</t>
-  </si>
-  <si>
-    <t>Realm应该是所有区共用的，所以单独放到一个zone</t>
   </si>
   <si>
     <t>Realm</t>
@@ -745,7 +725,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -756,9 +736,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1108,100 +1085,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="7"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.6283185840708" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.3716814159292" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.1238938053097" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
+    <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="13.125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="C3" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="3:8">
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>10</v>
+    <row r="5" spans="1:8">
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="3:8">
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="5" customFormat="1" spans="3:8">
+    <row r="6" customFormat="1" spans="1:8">
       <c r="C6" s="4">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
       </c>
       <c r="E6" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" s="4">
         <v>10101</v>
       </c>
     </row>
-    <row r="7" s="5" customFormat="1" spans="3:8">
+    <row r="7" customFormat="1" spans="1:8">
       <c r="C7" s="4">
-        <v>102</v>
+        <v>301</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1209,19 +1191,19 @@
       <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="G7" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="H7" s="4">
-        <v>10102</v>
+        <v>30101</v>
       </c>
     </row>
-    <row r="8" s="5" customFormat="1" spans="3:8">
+    <row r="8" spans="1:8">
       <c r="C8" s="4">
-        <v>103</v>
+        <v>302</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -1229,19 +1211,19 @@
       <c r="E8" s="4">
         <v>3</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>16</v>
+      <c r="F8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H8" s="4">
-        <v>10103</v>
+        <v>30102</v>
       </c>
     </row>
-    <row r="9" s="5" customFormat="1" spans="3:8">
+    <row r="9" spans="1:8">
       <c r="C9" s="4">
-        <v>104</v>
+        <v>303</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -1249,19 +1231,17 @@
       <c r="E9" s="4">
         <v>3</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="4">
-        <v>10104</v>
-      </c>
+      <c r="F9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="4"/>
     </row>
-    <row r="10" s="5" customFormat="1" spans="3:8">
+    <row r="10" spans="1:8">
       <c r="C10" s="4">
-        <v>105</v>
+        <v>304</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1269,287 +1249,31 @@
       <c r="E10" s="4">
         <v>3</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="4">
-        <v>10105</v>
-      </c>
+      <c r="F10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="4"/>
     </row>
-  </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="11" spans="1:8">
+      <c r="C11" s="4">
+        <v>305</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="3:8">
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="3:8">
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8">
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8">
-      <c r="C6" s="4">
-        <v>201</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="4">
-        <v>20101</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C3:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.6283185840708" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.3716814159292" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.1238938053097" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:8">
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="3:8">
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8">
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="13.5" spans="3:8">
-      <c r="C6" s="4">
-        <v>301</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="4">
-        <v>30101</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8">
-      <c r="C7" s="4">
-        <v>302</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="4">
-        <v>30102</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8">
-      <c r="C8" s="4">
-        <v>303</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="3:8">
-      <c r="C9" s="4">
-        <v>304</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="3:8">
-      <c r="C10" s="4">
-        <v>305</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="4"/>
+      <c r="H11" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ET/Packages/cn.etetet.statesync/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET/Packages/cn.etetet.statesync/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11025"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Scene" sheetId="1" r:id="rId1"/>
+    <sheet name="Scene" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>Realm应该是所有区共用的，所以单独放到一个zone</t>
   </si>
@@ -98,180 +87,203 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="300" formatCode="General"/>
+    <numFmt numFmtId="301" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="302" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="303" formatCode="0%"/>
+    <numFmt numFmtId="304" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="305" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
+  <fonts count="25">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <b val="true"/>
+      <color theme="1"/>
       <sz val="9"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="true"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="true"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="true"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="true"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="true"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="true"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="true"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="true"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="true"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,6 +297,9 @@
       </patternFill>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
@@ -334,19 +349,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -358,19 +373,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,19 +397,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,19 +421,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,19 +445,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,24 +469,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -508,7 +530,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.499985"/>
       </bottom>
       <diagonal/>
     </border>
@@ -578,174 +600,190 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  <cellStyleXfs>
+    <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="300" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="302" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="303" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="304" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="305" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="14" fillId="5" borderId="5" xfId="0" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="17" fillId="7" borderId="7" xfId="0" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="18" fillId="3" borderId="8" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="19" fillId="3" borderId="9" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="20" fillId="8" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="21" fillId="9" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="22" fillId="10" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="11" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="12" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="13" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="14" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="15" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="16" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="17" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="18" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="19" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="20" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="21" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="22" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="23" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="24" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="25" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="26" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="27" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="28" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="29" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="30" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="31" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="32" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="33" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="34" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="300" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="300" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="2" builtinId="3"/>
+    <cellStyle name="货币" xfId="3" builtinId="4"/>
+    <cellStyle name="百分比" xfId="4" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="6" builtinId="7"/>
     <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
     <cellStyle name="注释" xfId="8" builtinId="10"/>
     <cellStyle name="警告文本" xfId="9" builtinId="11"/>
@@ -789,12 +827,6 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -916,7 +948,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -937,9 +969,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="true"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -960,7 +992,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -989,7 +1021,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -998,7 +1030,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1007,7 +1039,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1030,7 +1062,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1056,7 +1088,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1083,200 +1115,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="XFD6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="21.125" style="9" customWidth="true"/>
+    <col min="2" max="2" width="12.75" style="9" customWidth="true"/>
+    <col min="3" max="5" width="12.625" style="10" customWidth="true"/>
+    <col min="6" max="6" width="15.375" style="10" customWidth="true"/>
+    <col min="7" max="8" width="13.125" style="10" customWidth="true"/>
+    <col min="9" max="26" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1" spans="1:1">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="3:8">
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8">
+      <c r="C4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8">
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" customFormat="true">
+      <c r="C6" s="6">
+        <v>301</v>
+      </c>
+      <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="E6" s="6">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:8">
-      <c r="C6" s="4">
-        <v>201</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="F6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="6">
         <v>10101</v>
       </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:8">
-      <c r="C7" s="4">
-        <v>301</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="4">
-        <v>30101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="C8" s="4">
-        <v>302</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="4">
-        <v>30102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="C9" s="4">
-        <v>303</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="C10" s="4">
-        <v>304</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="C11" s="4">
-        <v>305</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
